--- a/data/test/notes.xlsx
+++ b/data/test/notes.xlsx
@@ -397,10 +397,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:E2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>weekLabel</v>
+      </c>
+      <c r="C1" t="str">
+        <v>customerId</v>
+      </c>
+      <c r="D1" t="str">
+        <v>day</v>
+      </c>
+      <c r="E1" t="str">
+        <v>note</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-W20-0901000005-1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-W20</v>
+      </c>
+      <c r="C2" t="str">
+        <v>0901000005</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>lấy nhiều thịt nướng</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/test/notes.xlsx
+++ b/data/test/notes.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,24 +418,41 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-W20-0901000005-1</v>
+        <v>2026-W20-0901000013-1</v>
       </c>
       <c r="B2" t="str">
         <v>2026-W20</v>
       </c>
       <c r="C2" t="str">
-        <v>0901000005</v>
+        <v>0901000013</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>lấy nhiều thịt nướng</v>
+        <v>address change</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-W20-0368980079-1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-W20</v>
+      </c>
+      <c r="C3" t="str">
+        <v>0368980079</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Phong đẹp chai</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/test/notes.xlsx
+++ b/data/test/notes.xlsx
@@ -397,62 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>weekLabel</v>
-      </c>
-      <c r="C1" t="str">
-        <v>customerId</v>
-      </c>
-      <c r="D1" t="str">
-        <v>day</v>
-      </c>
-      <c r="E1" t="str">
-        <v>note</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-W20-0901000013-1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-W20</v>
-      </c>
-      <c r="C2" t="str">
-        <v>0901000013</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>address change</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2026-W20-0368980079-1</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-W20</v>
-      </c>
-      <c r="C3" t="str">
-        <v>0368980079</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Phong đẹp chai</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>